--- a/output/StructureDefinition-BRCID10Avaliado-1.0.xlsx
+++ b/output/StructureDefinition-BRCID10Avaliado-1.0.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3784" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3782" uniqueCount="573">
   <si>
     <t>Property</t>
   </si>
@@ -1048,6 +1048,15 @@
     <t>gender</t>
   </si>
   <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Sexo biológico obtido por meio de exame clínico ou de outros métodos diagnósticos referente ao indivíduo da hipótese de impossibilidade de identificação.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRSexo-1.0</t>
+  </si>
+  <si>
     <t>Condition.subject.extension:unidentifiedPatient.extension:gender.id</t>
   </si>
   <si>
@@ -1097,6 +1106,12 @@
   </si>
   <si>
     <t>birthYear</t>
+  </si>
+  <si>
+    <t>Ano de nascimento estimado</t>
+  </si>
+  <si>
+    <t>Estimativa do ano de nascimento por meio de observação direta da idade do indivíduo na hipótese de impossibilidade de identificação..</t>
   </si>
   <si>
     <t>Condition.subject.extension:unidentifiedPatient.extension:birthYear.id</t>
@@ -1119,6 +1134,15 @@
   </si>
   <si>
     <t>reason</t>
+  </si>
+  <si>
+    <t>Justificativa da impossibilidade de identificação do indivíduo</t>
+  </si>
+  <si>
+    <t>Razão pela qual não foi possível obter os dados de identificação do indivíduo no contato assistencial.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRJustificativaIndividuoNaoIdentificado-1.0</t>
   </si>
   <si>
     <t>Condition.subject.extension:unidentifiedPatient.extension:reason.id</t>
@@ -7583,10 +7607,10 @@
         <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7613,13 +7637,11 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7672,10 +7694,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7790,10 +7812,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7910,10 +7932,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7939,13 +7961,13 @@
         <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7995,7 +8017,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>92</v>
@@ -8030,10 +8052,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8059,10 +8081,10 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8113,7 +8135,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8148,13 +8170,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>325</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>79</v>
@@ -8179,10 +8201,10 @@
         <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>315</v>
+        <v>349</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8268,10 +8290,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8386,10 +8408,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8506,10 +8528,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8535,13 +8557,13 @@
         <v>105</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8549,7 +8571,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>79</v>
@@ -8591,7 +8613,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>92</v>
@@ -8626,10 +8648,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8652,13 +8674,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8709,7 +8731,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8744,13 +8766,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>325</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>79</v>
@@ -8775,10 +8797,10 @@
         <v>137</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>315</v>
+        <v>358</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>316</v>
+        <v>359</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8805,13 +8827,11 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8864,10 +8884,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8982,10 +9002,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9102,10 +9122,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9131,13 +9151,13 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9145,7 +9165,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>79</v>
@@ -9187,7 +9207,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>92</v>
@@ -9222,10 +9242,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9251,10 +9271,10 @@
         <v>158</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9305,7 +9325,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9340,10 +9360,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9369,13 +9389,13 @@
         <v>105</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9383,7 +9403,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>79</v>
@@ -9425,7 +9445,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>92</v>
@@ -9460,10 +9480,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9486,13 +9506,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9543,7 +9563,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9578,10 +9598,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9607,13 +9627,13 @@
         <v>172</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9663,7 +9683,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9672,7 +9692,7 @@
         <v>92</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>103</v>
@@ -9698,10 +9718,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9727,13 +9747,13 @@
         <v>105</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9741,7 +9761,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>79</v>
@@ -9759,13 +9779,13 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9783,7 +9803,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9818,10 +9838,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9847,13 +9867,13 @@
         <v>149</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9903,7 +9923,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9927,7 +9947,7 @@
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9938,10 +9958,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10056,10 +10076,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10176,10 +10196,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10205,16 +10225,16 @@
         <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10242,10 +10262,10 @@
         <v>162</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>79</v>
@@ -10263,7 +10283,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10287,7 +10307,7 @@
         <v>134</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>79</v>
@@ -10298,10 +10318,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10327,16 +10347,16 @@
         <v>158</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10361,13 +10381,13 @@
         <v>79</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
@@ -10385,7 +10405,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10406,10 +10426,10 @@
         <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10420,10 +10440,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10449,16 +10469,16 @@
         <v>105</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -10471,7 +10491,7 @@
         <v>79</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>79</v>
@@ -10507,7 +10527,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10528,10 +10548,10 @@
         <v>79</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10542,10 +10562,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10571,13 +10591,13 @@
         <v>172</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10591,7 +10611,7 @@
         <v>79</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>79</v>
@@ -10627,7 +10647,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10648,10 +10668,10 @@
         <v>79</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10662,10 +10682,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10688,13 +10708,13 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10745,7 +10765,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10766,10 +10786,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10780,10 +10800,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10806,16 +10826,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10865,7 +10885,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10886,10 +10906,10 @@
         <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10900,10 +10920,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10929,13 +10949,13 @@
         <v>172</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10985,7 +11005,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11020,10 +11040,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11046,16 +11066,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11105,7 +11125,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11120,19 +11140,19 @@
         <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>79</v>
@@ -11140,10 +11160,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11166,16 +11186,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11225,7 +11245,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11240,19 +11260,19 @@
         <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>79</v>
@@ -11260,10 +11280,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11286,16 +11306,16 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11345,7 +11365,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11354,7 +11374,7 @@
         <v>92</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>103</v>
@@ -11369,10 +11389,10 @@
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>79</v>
@@ -11380,10 +11400,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11406,13 +11426,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11463,7 +11483,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11484,13 +11504,13 @@
         <v>79</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>79</v>
@@ -11498,10 +11518,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11524,13 +11544,13 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11581,7 +11601,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11605,10 +11625,10 @@
         <v>79</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>79</v>
@@ -11616,10 +11636,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11642,13 +11662,13 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11699,7 +11719,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11720,13 +11740,13 @@
         <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>79</v>
@@ -11734,10 +11754,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11760,13 +11780,13 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11817,7 +11837,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11829,7 +11849,7 @@
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
@@ -11841,7 +11861,7 @@
         <v>79</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -11852,10 +11872,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11970,10 +11990,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12090,14 +12110,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12119,10 +12139,10 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>140</v>
@@ -12177,7 +12197,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12212,10 +12232,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12241,10 +12261,10 @@
         <v>158</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12274,10 +12294,10 @@
         <v>297</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>79</v>
@@ -12295,7 +12315,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12304,7 +12324,7 @@
         <v>92</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -12313,7 +12333,7 @@
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>168</v>
@@ -12330,10 +12350,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12356,13 +12376,13 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12413,7 +12433,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12422,7 +12442,7 @@
         <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>103</v>
@@ -12437,7 +12457,7 @@
         <v>79</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>79</v>
@@ -12448,10 +12468,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12477,10 +12497,10 @@
         <v>158</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12510,10 +12530,10 @@
         <v>297</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>79</v>
@@ -12531,7 +12551,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12555,7 +12575,7 @@
         <v>79</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12566,10 +12586,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12592,16 +12612,16 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12651,7 +12671,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12663,7 +12683,7 @@
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>79</v>
@@ -12675,7 +12695,7 @@
         <v>79</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>79</v>
@@ -12686,10 +12706,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12804,10 +12824,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12924,14 +12944,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12953,10 +12973,10 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>140</v>
@@ -13011,7 +13031,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13046,10 +13066,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13075,10 +13095,10 @@
         <v>158</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13108,10 +13128,10 @@
         <v>297</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13129,7 +13149,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13138,13 +13158,13 @@
         <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>256</v>
@@ -13153,10 +13173,10 @@
         <v>79</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>79</v>
@@ -13164,10 +13184,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13190,13 +13210,13 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13247,7 +13267,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13256,7 +13276,7 @@
         <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>103</v>
@@ -13271,10 +13291,10 @@
         <v>79</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -13282,10 +13302,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13308,13 +13328,13 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13365,7 +13385,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13380,16 +13400,16 @@
         <v>103</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>79</v>
@@ -13400,10 +13420,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13518,10 +13538,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13638,10 +13658,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13664,16 +13684,16 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13723,7 +13743,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13747,7 +13767,7 @@
         <v>134</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>79</v>
@@ -13758,10 +13778,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13784,13 +13804,13 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13841,7 +13861,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13865,7 +13885,7 @@
         <v>134</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>79</v>
@@ -13876,10 +13896,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13902,13 +13922,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13959,7 +13979,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>92</v>
@@ -13983,7 +14003,7 @@
         <v>134</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>79</v>
